--- a/Math/Методы Деления на пополам, хорд, золотого сечения.xlsx
+++ b/Math/Методы Деления на пополам, хорд, золотого сечения.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nazar\Documents\study\P-8-24-Study\3й курс\Math\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nazar\Documents\study\P-8-24-Study\3 Kypc\Math\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E4A2E26-1423-43DD-9076-4B33550F3F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68BF4CE2-B3F0-445D-957F-7D93192C6532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="16200" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="16200" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="метод деления на два" sheetId="1" r:id="rId1"/>
-    <sheet name="Метод золотого сечения " sheetId="2" r:id="rId2"/>
-    <sheet name="Мктод хорд" sheetId="3" r:id="rId3"/>
+    <sheet name="Метод хорд" sheetId="3" r:id="rId2"/>
+    <sheet name="Метод золотого сечения " sheetId="2" r:id="rId3"/>
     <sheet name="метод простых итераций" sheetId="4" r:id="rId4"/>
     <sheet name="мотод ньютена" sheetId="5" r:id="rId5"/>
   </sheets>
@@ -116,7 +116,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="0.00000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -176,13 +176,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -458,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -502,7 +513,7 @@
         <v>0.5</v>
       </c>
       <c r="D2">
-        <f>(A2^3 )+A2 -1</f>
+        <f>A2^3 + 3*A2 - 1</f>
         <v>-1</v>
       </c>
       <c r="E2">
@@ -510,8 +521,8 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <f>(C2^3)+C2 -1</f>
-        <v>-0.375</v>
+        <f>C2^3 + 3*C2 - 1</f>
+        <v>0.625</v>
       </c>
       <c r="H2">
         <v>0.01</v>
@@ -519,32 +530,1264 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3">
+        <f>IF(D2*F2&lt;0, A2, C2)</f>
+        <v>0</v>
+      </c>
+      <c r="B3">
+        <f>IF(D2*F2&lt;0, C2, B2)</f>
+        <v>0.5</v>
+      </c>
+      <c r="C3">
+        <f>(A3+B3)/2</f>
+        <v>0.25</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ref="D3" si="0">A3^3 + 3*A3 - 1</f>
+        <v>-1</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3" si="1">(B3^3)+B3-1</f>
+        <v>-0.375</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3" si="2">C3^3 + 3*C3 - 1</f>
+        <v>-0.234375</v>
+      </c>
+      <c r="G3">
+        <f>ABS(B3-A3)</f>
+        <v>0.5</v>
+      </c>
+      <c r="H3">
+        <v>0.01</v>
+      </c>
+      <c r="I3" t="str">
+        <f>IF(G3&lt;H3, C3, "Не ответ")</f>
+        <v>Не ответ</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <f t="shared" ref="A4:A33" si="3">IF(D3*F3&lt;0, A3, C3)</f>
+        <v>0.25</v>
+      </c>
+      <c r="B4">
+        <f t="shared" ref="B4:B33" si="4">IF(D3*F3&lt;0, C3, B3)</f>
+        <v>0.5</v>
+      </c>
+      <c r="C4">
+        <f t="shared" ref="C4:C33" si="5">(A4+B4)/2</f>
+        <v>0.375</v>
+      </c>
+      <c r="D4">
+        <f t="shared" ref="D4:D33" si="6">A4^3 + 3*A4 - 1</f>
+        <v>-0.234375</v>
+      </c>
+      <c r="E4">
+        <f t="shared" ref="E4:E33" si="7">(B4^3)+B4-1</f>
+        <v>-0.375</v>
+      </c>
+      <c r="F4">
+        <f t="shared" ref="F4:F33" si="8">C4^3 + 3*C4 - 1</f>
+        <v>0.177734375</v>
+      </c>
+      <c r="G4">
+        <f t="shared" ref="G4:G33" si="9">ABS(B4-A4)</f>
+        <v>0.25</v>
+      </c>
+      <c r="H4">
+        <v>0.01</v>
+      </c>
+      <c r="I4" t="str">
+        <f t="shared" ref="I4:I33" si="10">IF(G4&lt;H4, C4, "Не ответ")</f>
+        <v>Не ответ</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="4"/>
+        <v>0.375</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="5"/>
+        <v>0.3125</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="6"/>
+        <v>-0.234375</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="7"/>
+        <v>-0.572265625</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="8"/>
+        <v>-3.1982421875E-2</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="H5">
+        <v>0.01</v>
+      </c>
+      <c r="I5" t="str">
+        <f t="shared" si="10"/>
+        <v>Не ответ</v>
+      </c>
+      <c r="M5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <f t="shared" si="3"/>
+        <v>0.3125</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="4"/>
+        <v>0.375</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="5"/>
+        <v>0.34375</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="6"/>
+        <v>-3.1982421875E-2</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="7"/>
+        <v>-0.572265625</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="8"/>
+        <v>7.1868896484375E-2</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="9"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="H6">
+        <v>0.01</v>
+      </c>
+      <c r="I6" t="str">
+        <f t="shared" si="10"/>
+        <v>Не ответ</v>
+      </c>
+      <c r="M6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <f t="shared" si="3"/>
+        <v>0.3125</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="4"/>
+        <v>0.34375</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="5"/>
+        <v>0.328125</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="6"/>
+        <v>-3.1982421875E-2</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="7"/>
+        <v>-0.615631103515625</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="8"/>
+        <v>1.9702911376953125E-2</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="9"/>
+        <v>3.125E-2</v>
+      </c>
+      <c r="H7">
+        <v>0.01</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="10"/>
+        <v>Не ответ</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <f t="shared" si="3"/>
+        <v>0.3125</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="4"/>
+        <v>0.328125</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="5"/>
+        <v>0.3203125</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="6"/>
+        <v>-3.1982421875E-2</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="7"/>
+        <v>-0.63654708862304688</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="8"/>
+        <v>-6.1984062194824219E-3</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="9"/>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H8">
+        <v>0.01</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="10"/>
+        <v>Не ответ</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <f t="shared" si="3"/>
+        <v>0.3203125</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="4"/>
+        <v>0.328125</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="5"/>
+        <v>0.32421875</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="6"/>
+        <v>-6.1984062194824219E-3</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="7"/>
+        <v>-0.63654708862304688</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="8"/>
+        <v>6.7374110221862793E-3</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="9"/>
+        <v>7.8125E-3</v>
+      </c>
+      <c r="H9">
+        <v>0.01</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="10"/>
+        <v>0.32421875</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <f t="shared" si="3"/>
+        <v>0.3203125</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="4"/>
+        <v>0.32421875</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="5"/>
+        <v>0.322265625</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="6"/>
+        <v>-6.1984062194824219E-3</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="7"/>
+        <v>-0.64170008897781372</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="8"/>
+        <v>2.6581436395645142E-4</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="9"/>
+        <v>3.90625E-3</v>
+      </c>
+      <c r="H10">
+        <v>0.01</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="10"/>
+        <v>0.322265625</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <f t="shared" si="3"/>
+        <v>0.3203125</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="4"/>
+        <v>0.322265625</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="5"/>
+        <v>0.3212890625</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="6"/>
+        <v>-6.1984062194824219E-3</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="7"/>
+        <v>-0.64426543563604355</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="8"/>
+        <v>-2.9672151431441307E-3</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="9"/>
+        <v>1.953125E-3</v>
+      </c>
+      <c r="H11">
+        <v>0.01</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="10"/>
+        <v>0.3212890625</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <f t="shared" si="3"/>
+        <v>0.3212890625</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="4"/>
+        <v>0.322265625</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="5"/>
+        <v>0.32177734375</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="6"/>
+        <v>-2.9672151431441307E-3</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="7"/>
+        <v>-0.64426543563604355</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="8"/>
+        <v>-1.3509305426850915E-3</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="9"/>
+        <v>9.765625E-4</v>
+      </c>
+      <c r="H12">
+        <v>0.01</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="10"/>
+        <v>0.32177734375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <f t="shared" si="3"/>
+        <v>0.32177734375</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="4"/>
+        <v>0.322265625</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="5"/>
+        <v>0.322021484375</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="6"/>
+        <v>-1.3509305426850915E-3</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="7"/>
+        <v>-0.64426543563604355</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="8"/>
+        <v>-5.4261567129287869E-4</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="9"/>
+        <v>4.8828125E-4</v>
+      </c>
+      <c r="H13">
+        <v>0.01</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="10"/>
+        <v>0.322021484375</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <f t="shared" si="3"/>
+        <v>0.322021484375</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="4"/>
+        <v>0.322265625</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="5"/>
+        <v>0.3221435546875</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="6"/>
+        <v>-5.4261567129287869E-4</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="7"/>
+        <v>-0.64426543563604355</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="8"/>
+        <v>-1.3841505460732151E-4</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="9"/>
+        <v>2.44140625E-4</v>
+      </c>
+      <c r="H14">
+        <v>0.01</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="10"/>
+        <v>0.3221435546875</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <f t="shared" si="3"/>
+        <v>0.3221435546875</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="4"/>
+        <v>0.322265625</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="5"/>
+        <v>0.32220458984375</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="6"/>
+        <v>-1.3841505460732151E-4</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="7"/>
+        <v>-0.64426543563604355</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="8"/>
+        <v>6.3696053757666959E-5</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="9"/>
+        <v>1.220703125E-4</v>
+      </c>
+      <c r="H15">
+        <v>0.01</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="10"/>
+        <v>0.32220458984375</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <f t="shared" si="3"/>
+        <v>0.3221435546875</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="4"/>
+        <v>0.32220458984375</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="5"/>
+        <v>0.322174072265625</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="6"/>
+        <v>-1.3841505460732151E-4</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="7"/>
+        <v>-0.64434548363374233</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="8"/>
+        <v>-3.7360400568786645E-5</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="9"/>
+        <v>6.103515625E-5</v>
+      </c>
+      <c r="H16">
+        <v>0.01</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="10"/>
+        <v>0.322174072265625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <f t="shared" si="3"/>
+        <v>0.322174072265625</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="4"/>
+        <v>0.32220458984375</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="5"/>
+        <v>0.3221893310546875</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="6"/>
+        <v>-3.7360400568786645E-5</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="7"/>
+        <v>-0.64434548363374233</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="8"/>
+        <v>1.3167601547792174E-5</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="9"/>
+        <v>3.0517578125E-5</v>
+      </c>
+      <c r="H17">
+        <v>0.01</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="10"/>
+        <v>0.3221893310546875</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <f t="shared" si="3"/>
+        <v>0.322174072265625</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="4"/>
+        <v>0.3221893310546875</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="5"/>
+        <v>0.32218170166015625</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="6"/>
+        <v>-3.7360400568786645E-5</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="7"/>
+        <v>-0.64436549450782721</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="8"/>
+        <v>-1.2096455770826964E-5</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="9"/>
+        <v>1.52587890625E-5</v>
+      </c>
+      <c r="H18">
+        <v>0.01</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="10"/>
+        <v>0.32218170166015625</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <f t="shared" si="3"/>
+        <v>0.32218170166015625</v>
+      </c>
+      <c r="B19">
+        <f t="shared" si="4"/>
+        <v>0.3221893310546875</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="5"/>
+        <v>0.32218551635742188</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="6"/>
+        <v>-1.2096455770826964E-5</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="7"/>
+        <v>-0.64436549450782721</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="8"/>
+        <v>5.3555882328915061E-7</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="9"/>
+        <v>7.62939453125E-6</v>
+      </c>
+      <c r="H19">
+        <v>0.01</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="10"/>
+        <v>0.32218551635742188</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <f t="shared" si="3"/>
+        <v>0.32218170166015625</v>
+      </c>
+      <c r="B20">
+        <f t="shared" si="4"/>
+        <v>0.32218551635742188</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="5"/>
+        <v>0.32218360900878906</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="6"/>
+        <v>-1.2096455770826964E-5</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="7"/>
+        <v>-0.64437049715602046</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="8"/>
+        <v>-5.7804519900672702E-6</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="9"/>
+        <v>3.814697265625E-6</v>
+      </c>
+      <c r="H20">
+        <v>0.01</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="10"/>
+        <v>0.32218360900878906</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <f t="shared" si="3"/>
+        <v>0.32218360900878906</v>
+      </c>
+      <c r="B21">
+        <f t="shared" si="4"/>
+        <v>0.32218551635742188</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="5"/>
+        <v>0.32218456268310547</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="6"/>
+        <v>-5.7804519900672702E-6</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="7"/>
+        <v>-0.64437049715602046</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="8"/>
+        <v>-2.6224474625191618E-6</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="9"/>
+        <v>1.9073486328125E-6</v>
+      </c>
+      <c r="H21">
+        <v>0.01</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="10"/>
+        <v>0.32218456268310547</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <f t="shared" si="3"/>
+        <v>0.32218456268310547</v>
+      </c>
+      <c r="B22">
+        <f t="shared" si="4"/>
+        <v>0.32218551635742188</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="5"/>
+        <v>0.32218503952026367</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="6"/>
+        <v>-2.6224474625191618E-6</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="7"/>
+        <v>-0.64437049715602046</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="8"/>
+        <v>-1.0434445394391645E-6</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="9"/>
+        <v>9.5367431640625E-7</v>
+      </c>
+      <c r="H22">
+        <v>0.01</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="10"/>
+        <v>0.32218503952026367</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <f t="shared" si="3"/>
+        <v>0.32218503952026367</v>
+      </c>
+      <c r="B23">
+        <f t="shared" si="4"/>
+        <v>0.32218551635742188</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="5"/>
+        <v>0.32218527793884277</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="6"/>
+        <v>-1.0434445394391645E-6</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="7"/>
+        <v>-0.64437049715602046</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="8"/>
+        <v>-2.5394291303104666E-7</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="9"/>
+        <v>4.76837158203125E-7</v>
+      </c>
+      <c r="H23">
+        <v>0.01</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="10"/>
+        <v>0.32218527793884277</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <f t="shared" si="3"/>
+        <v>0.32218527793884277</v>
+      </c>
+      <c r="B24">
+        <f t="shared" si="4"/>
+        <v>0.32218551635742188</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="5"/>
+        <v>0.32218539714813232</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="6"/>
+        <v>-2.5394291303104666E-7</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="7"/>
+        <v>-0.64437049715602046</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="8"/>
+        <v>1.4080794130677532E-7</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="9"/>
+        <v>2.384185791015625E-7</v>
+      </c>
+      <c r="H24">
+        <v>0.01</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="10"/>
+        <v>0.32218539714813232</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <f t="shared" si="3"/>
+        <v>0.32218527793884277</v>
+      </c>
+      <c r="B25">
+        <f t="shared" si="4"/>
+        <v>0.32218539714813232</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="5"/>
+        <v>0.32218533754348755</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="6"/>
+        <v>-2.5394291303104666E-7</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="7"/>
+        <v>-0.64437065348832334</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="8"/>
+        <v>-5.6567489248315894E-8</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="9"/>
+        <v>1.1920928955078125E-7</v>
+      </c>
+      <c r="H25">
+        <v>0.01</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="10"/>
+        <v>0.32218533754348755</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <f t="shared" si="3"/>
+        <v>0.32218533754348755</v>
+      </c>
+      <c r="B26">
+        <f t="shared" si="4"/>
+        <v>0.32218539714813232</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="5"/>
+        <v>0.32218536734580994</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="6"/>
+        <v>-5.6567489248315894E-8</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="7"/>
+        <v>-0.64437065348832334</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="8"/>
+        <v>4.2120225085540142E-8</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="9"/>
+        <v>5.9604644775390625E-8</v>
+      </c>
+      <c r="H26">
+        <v>0.01</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="10"/>
+        <v>0.32218536734580994</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <f t="shared" si="3"/>
+        <v>0.32218533754348755</v>
+      </c>
+      <c r="B27">
+        <f t="shared" si="4"/>
+        <v>0.32218536734580994</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="5"/>
+        <v>0.32218535244464874</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="6"/>
+        <v>-5.6567489248315894E-8</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="7"/>
+        <v>-0.64437069257139468</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="8"/>
+        <v>-7.22363224792133E-9</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="9"/>
+        <v>2.9802322387695313E-8</v>
+      </c>
+      <c r="H27">
+        <v>0.01</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="10"/>
+        <v>0.32218535244464874</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <f t="shared" si="3"/>
+        <v>0.32218535244464874</v>
+      </c>
+      <c r="B28">
+        <f t="shared" si="4"/>
+        <v>0.32218536734580994</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="5"/>
+        <v>0.32218535989522934</v>
+      </c>
+      <c r="D28">
+        <f t="shared" si="6"/>
+        <v>-7.22363224792133E-9</v>
+      </c>
+      <c r="E28">
+        <f t="shared" si="7"/>
+        <v>-0.64437069257139468</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="8"/>
+        <v>1.7448296363298255E-8</v>
+      </c>
+      <c r="G28">
+        <f t="shared" si="9"/>
+        <v>1.4901161193847656E-8</v>
+      </c>
+      <c r="H28">
+        <v>0.01</v>
+      </c>
+      <c r="I28">
+        <f t="shared" si="10"/>
+        <v>0.32218535989522934</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <f t="shared" si="3"/>
+        <v>0.32218535244464874</v>
+      </c>
+      <c r="B29">
+        <f t="shared" si="4"/>
+        <v>0.32218535989522934</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="5"/>
+        <v>0.32218535616993904</v>
+      </c>
+      <c r="D29">
+        <f t="shared" si="6"/>
+        <v>-7.22363224792133E-9</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="7"/>
+        <v>-0.64437070234216232</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="8"/>
+        <v>5.1123321131996136E-9</v>
+      </c>
+      <c r="G29">
+        <f t="shared" si="9"/>
+        <v>7.4505805969238281E-9</v>
+      </c>
+      <c r="H29">
+        <v>0.01</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="10"/>
+        <v>0.32218535616993904</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <f t="shared" si="3"/>
+        <v>0.32218535244464874</v>
+      </c>
+      <c r="B30">
+        <f t="shared" si="4"/>
+        <v>0.32218535616993904</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="5"/>
+        <v>0.32218535430729389</v>
+      </c>
+      <c r="D30">
+        <f t="shared" si="6"/>
+        <v>-7.22363224792133E-9</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="7"/>
+        <v>-0.64437070722754597</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="8"/>
+        <v>-1.0556501228720094E-9</v>
+      </c>
+      <c r="G30">
+        <f t="shared" si="9"/>
+        <v>3.7252902984619141E-9</v>
+      </c>
+      <c r="H30">
+        <v>0.01</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="10"/>
+        <v>0.32218535430729389</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <f t="shared" si="3"/>
+        <v>0.32218535430729389</v>
+      </c>
+      <c r="B31">
+        <f t="shared" si="4"/>
+        <v>0.32218535616993904</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="5"/>
+        <v>0.32218535523861647</v>
+      </c>
+      <c r="D31">
+        <f t="shared" si="6"/>
+        <v>-1.0556501228720094E-9</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="7"/>
+        <v>-0.64437070722754597</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="8"/>
+        <v>2.0283410506749533E-9</v>
+      </c>
+      <c r="G31">
+        <f t="shared" si="9"/>
+        <v>1.862645149230957E-9</v>
+      </c>
+      <c r="H31">
+        <v>0.01</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="10"/>
+        <v>0.32218535523861647</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <f t="shared" si="3"/>
+        <v>0.32218535430729389</v>
+      </c>
+      <c r="B32">
+        <f t="shared" si="4"/>
+        <v>0.32218535523861647</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="5"/>
+        <v>0.32218535477295518</v>
+      </c>
+      <c r="D32">
+        <f t="shared" si="6"/>
+        <v>-1.0556501228720094E-9</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="7"/>
+        <v>-0.64437070844889188</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="8"/>
+        <v>4.863454083903207E-10</v>
+      </c>
+      <c r="G32">
+        <f t="shared" si="9"/>
+        <v>9.3132257461547852E-10</v>
+      </c>
+      <c r="H32">
+        <v>0.01</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="10"/>
+        <v>0.32218535477295518</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <f t="shared" si="3"/>
+        <v>0.32218535430729389</v>
+      </c>
+      <c r="B33">
+        <f t="shared" si="4"/>
+        <v>0.32218535477295518</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="5"/>
+        <v>0.32218535454012454</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="6"/>
+        <v>-1.0556501228720094E-9</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="7"/>
+        <v>-0.64437070905956495</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="8"/>
+        <v>-2.8465230172969314E-10</v>
+      </c>
+      <c r="G33">
+        <f t="shared" si="9"/>
+        <v>4.6566128730773926E-10</v>
+      </c>
+      <c r="H33">
+        <v>0.01</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="10"/>
+        <v>0.32218535454012454</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I1:I1048576">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Ответ">
+      <formula>NOT(ISERROR(SEARCH("Ответ",I1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{854C4007-B242-4866-BDB4-E9D073D572EC}">
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <f>(A2*E2-B2*D2)/(E2-D2)</f>
+        <v>0.25</v>
+      </c>
+      <c r="D2">
+        <f t="shared" ref="D2:F3" si="0">A2^3+3*A2-1</f>
+        <v>-1</v>
+      </c>
+      <c r="E2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <f t="shared" si="0"/>
+        <v>-0.234375</v>
+      </c>
+      <c r="G2">
+        <f>ABS(C2-A2)</f>
+        <v>0.25</v>
+      </c>
+      <c r="H2">
+        <v>0.01</v>
+      </c>
+      <c r="I2" t="str">
+        <f>IF(G2&lt;H2, C2, "Не ответ")</f>
+        <v>Не ответ</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3">
         <f>IF(D2*F2&lt;0,A2,C2)</f>
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="B3">
         <f>IF(D2*F2&lt;0,C2,B2)</f>
         <v>1</v>
       </c>
       <c r="C3">
-        <f>(A3+B3)/2</f>
-        <v>0.75</v>
+        <f>(A3*E3-B3*D3)/(E3-D3)</f>
+        <v>0.30434782608695654</v>
       </c>
       <c r="D3">
-        <f>(A3^3 )+A3 -1</f>
-        <v>-0.375</v>
+        <f t="shared" si="0"/>
+        <v>-0.234375</v>
       </c>
       <c r="E3">
-        <f>(B3^3)+B3-1</f>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="F3">
-        <f>(C3^3)+C3 -1</f>
-        <v>0.171875</v>
+        <f t="shared" si="0"/>
+        <v>-5.8765513273608905E-2</v>
       </c>
       <c r="G3">
-        <f>ABS(C2-C3)</f>
-        <v>0.25</v>
+        <f>ABS(C3-A3)</f>
+        <v>5.4347826086956541E-2</v>
       </c>
       <c r="H3">
         <v>0.01</v>
@@ -554,528 +1797,670 @@
         <v>Не ответ</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
-        <f t="shared" ref="A4:A10" si="0">IF(D3*F3&lt;0,A3,C3)</f>
-        <v>0.5</v>
+        <f t="shared" ref="A4:A21" si="1">IF(D3*F3&lt;0,A3,C3)</f>
+        <v>0.30434782608695654</v>
       </c>
       <c r="B4">
-        <f t="shared" ref="B4:B10" si="1">IF(D3*F3&lt;0,C3,B3)</f>
-        <v>0.75</v>
+        <f t="shared" ref="B4:B21" si="2">IF(D3*F3&lt;0,C3,B3)</f>
+        <v>1</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:C10" si="2">(A4+B4)/2</f>
-        <v>0.625</v>
+        <f t="shared" ref="C4:C21" si="3">(A4*E4-B4*D4)/(E4-D4)</f>
+        <v>0.31771281169389515</v>
       </c>
       <c r="D4">
-        <f t="shared" ref="D4:D10" si="3">(A4^3 )+A4 -1</f>
-        <v>-0.375</v>
+        <f t="shared" ref="D4:D21" si="4">A4^3+3*A4-1</f>
+        <v>-5.8765513273608905E-2</v>
       </c>
       <c r="E4">
-        <f t="shared" ref="E4:E10" si="4">(B4^3)+B4-1</f>
-        <v>0.171875</v>
+        <f t="shared" ref="E4:E21" si="5">B4^3+3*B4-1</f>
+        <v>3</v>
       </c>
       <c r="F4">
-        <f t="shared" ref="F4:F10" si="5">(C4^3)+C4 -1</f>
-        <v>-0.130859375</v>
+        <f t="shared" ref="F4:F21" si="6">C4^3+3*C4-1</f>
+        <v>-1.4791179149625244E-2</v>
       </c>
       <c r="G4">
-        <f t="shared" ref="G4:G10" si="6">ABS(C3-C4)</f>
-        <v>0.125</v>
+        <f t="shared" ref="G4:G21" si="7">ABS(C4-A4)</f>
+        <v>1.3364985606938606E-2</v>
       </c>
       <c r="H4">
         <v>0.01</v>
       </c>
       <c r="I4" t="str">
-        <f t="shared" ref="I4:I17" si="7">IF(G4&lt;H4, C4, "Не ответ")</f>
+        <f t="shared" ref="I4:I21" si="8">IF(G4&lt;H4, C4, "Не ответ")</f>
         <v>Не ответ</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
-        <f t="shared" si="0"/>
-        <v>0.625</v>
+        <f t="shared" si="1"/>
+        <v>0.31771281169389515</v>
       </c>
       <c r="B5">
-        <f t="shared" si="1"/>
-        <v>0.75</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="C5">
-        <f t="shared" si="2"/>
-        <v>0.6875</v>
+        <f t="shared" si="3"/>
+        <v>0.3210602515111286</v>
       </c>
       <c r="D5">
-        <f t="shared" si="3"/>
-        <v>-0.130859375</v>
+        <f t="shared" si="4"/>
+        <v>-1.4791179149625244E-2</v>
       </c>
       <c r="E5">
-        <f t="shared" si="4"/>
-        <v>0.171875</v>
+        <f t="shared" si="5"/>
+        <v>3</v>
       </c>
       <c r="F5">
-        <f t="shared" si="5"/>
-        <v>1.2451171875E-2</v>
+        <f t="shared" si="6"/>
+        <v>-3.7244558425952867E-3</v>
       </c>
       <c r="G5">
-        <f t="shared" si="6"/>
-        <v>6.25E-2</v>
+        <f t="shared" si="7"/>
+        <v>3.3474398172334552E-3</v>
       </c>
       <c r="H5">
         <v>0.01</v>
       </c>
-      <c r="I5" t="str">
-        <f t="shared" si="7"/>
-        <v>Не ответ</v>
-      </c>
-      <c r="M5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I5">
+        <f t="shared" si="8"/>
+        <v>0.3210602515111286</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
-        <f t="shared" si="0"/>
-        <v>0.625</v>
+        <f t="shared" si="1"/>
+        <v>0.3210602515111286</v>
       </c>
       <c r="B6">
-        <f t="shared" si="1"/>
-        <v>0.6875</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="C6">
-        <f t="shared" si="2"/>
-        <v>0.65625</v>
+        <f t="shared" si="3"/>
+        <v>0.32190210007287368</v>
       </c>
       <c r="D6">
-        <f t="shared" si="3"/>
-        <v>-0.130859375</v>
+        <f t="shared" si="4"/>
+        <v>-3.7244558425952867E-3</v>
       </c>
       <c r="E6">
-        <f t="shared" si="4"/>
-        <v>1.2451171875E-2</v>
+        <f t="shared" si="5"/>
+        <v>3</v>
       </c>
       <c r="F6">
-        <f t="shared" si="5"/>
-        <v>-6.1126708984375E-2</v>
+        <f t="shared" si="6"/>
+        <v>-9.3789449192349661E-4</v>
       </c>
       <c r="G6">
-        <f t="shared" si="6"/>
-        <v>3.125E-2</v>
+        <f t="shared" si="7"/>
+        <v>8.4184856174507328E-4</v>
       </c>
       <c r="H6">
         <v>0.01</v>
       </c>
-      <c r="I6" t="str">
-        <f t="shared" si="7"/>
-        <v>Не ответ</v>
-      </c>
-      <c r="M6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I6">
+        <f t="shared" si="8"/>
+        <v>0.32190210007287368</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
-        <f t="shared" si="0"/>
-        <v>0.65625</v>
+        <f t="shared" si="1"/>
+        <v>0.32190210007287368</v>
       </c>
       <c r="B7">
-        <f t="shared" si="1"/>
-        <v>0.6875</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="C7">
-        <f t="shared" si="2"/>
-        <v>0.671875</v>
+        <f t="shared" si="3"/>
+        <v>0.32211402857912297</v>
       </c>
       <c r="D7">
-        <f t="shared" si="3"/>
-        <v>-6.1126708984375E-2</v>
+        <f t="shared" si="4"/>
+        <v>-9.3789449192349661E-4</v>
       </c>
       <c r="E7">
-        <f t="shared" si="4"/>
-        <v>1.2451171875E-2</v>
+        <f t="shared" si="5"/>
+        <v>3</v>
       </c>
       <c r="F7">
-        <f t="shared" si="5"/>
-        <v>-2.4829864501953125E-2</v>
+        <f t="shared" si="6"/>
+        <v>-2.3618488312382446E-4</v>
       </c>
       <c r="G7">
-        <f t="shared" si="6"/>
-        <v>1.5625E-2</v>
+        <f t="shared" si="7"/>
+        <v>2.119285062492926E-4</v>
       </c>
       <c r="H7">
         <v>0.01</v>
       </c>
-      <c r="I7" t="str">
-        <f t="shared" si="7"/>
-        <v>Не ответ</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I7">
+        <f t="shared" si="8"/>
+        <v>0.32211402857912297</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
-        <f t="shared" si="0"/>
-        <v>0.671875</v>
+        <f t="shared" si="1"/>
+        <v>0.32211402857912297</v>
       </c>
       <c r="B8">
-        <f t="shared" si="1"/>
-        <v>0.6875</v>
-      </c>
-      <c r="C8" s="1">
-        <f t="shared" si="2"/>
-        <v>0.6796875</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="3"/>
+        <v>0.32216739318412907</v>
       </c>
       <c r="D8">
-        <f t="shared" si="3"/>
-        <v>-2.4829864501953125E-2</v>
+        <f t="shared" si="4"/>
+        <v>-2.3618488312382446E-4</v>
       </c>
       <c r="E8">
-        <f t="shared" si="4"/>
-        <v>1.2451171875E-2</v>
+        <f t="shared" si="5"/>
+        <v>3</v>
       </c>
       <c r="F8">
-        <f t="shared" si="5"/>
-        <v>-6.3138008117675781E-3</v>
+        <f t="shared" si="6"/>
+        <v>-5.9477390430884292E-5</v>
       </c>
       <c r="G8">
-        <f t="shared" si="6"/>
-        <v>7.8125E-3</v>
+        <f t="shared" si="7"/>
+        <v>5.3364605006100962E-5</v>
       </c>
       <c r="H8">
         <v>0.01</v>
       </c>
       <c r="I8">
-        <f t="shared" si="7"/>
-        <v>0.6796875</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+        <f t="shared" si="8"/>
+        <v>0.32216739318412907</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
-        <f t="shared" si="0"/>
-        <v>0.6796875</v>
+        <f t="shared" si="1"/>
+        <v>0.32216739318412907</v>
       </c>
       <c r="B9">
-        <f t="shared" si="1"/>
-        <v>0.6875</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="C9">
-        <f t="shared" si="2"/>
-        <v>0.68359375</v>
+        <f t="shared" si="3"/>
+        <v>0.32218083148923804</v>
       </c>
       <c r="D9">
-        <f t="shared" si="3"/>
-        <v>-6.3138008117675781E-3</v>
+        <f t="shared" si="4"/>
+        <v>-5.9477390430884292E-5</v>
       </c>
       <c r="E9">
-        <f t="shared" si="4"/>
-        <v>1.2451171875E-2</v>
+        <f t="shared" si="5"/>
+        <v>3</v>
       </c>
       <c r="F9">
-        <f t="shared" si="5"/>
-        <v>3.0373930931091309E-3</v>
+        <f t="shared" si="6"/>
+        <v>-1.4977941755645041E-5</v>
       </c>
       <c r="G9">
-        <f t="shared" si="6"/>
-        <v>3.90625E-3</v>
+        <f t="shared" si="7"/>
+        <v>1.3438305108970372E-5</v>
       </c>
       <c r="H9">
         <v>0.01</v>
       </c>
       <c r="I9">
-        <f t="shared" si="7"/>
-        <v>0.68359375</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+        <f t="shared" si="8"/>
+        <v>0.32218083148923804</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
-        <f t="shared" si="0"/>
-        <v>0.6796875</v>
+        <f t="shared" si="1"/>
+        <v>0.32218083148923804</v>
       </c>
       <c r="B10">
-        <f t="shared" si="1"/>
-        <v>0.68359375</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="C10">
-        <f t="shared" si="2"/>
-        <v>0.681640625</v>
+        <f t="shared" si="3"/>
+        <v>0.3221842155843514</v>
       </c>
       <c r="D10">
-        <f t="shared" si="3"/>
-        <v>-6.3138008117675781E-3</v>
+        <f t="shared" si="4"/>
+        <v>-1.4977941755645041E-5</v>
       </c>
       <c r="E10">
-        <f t="shared" si="4"/>
-        <v>3.0373930931091309E-3</v>
+        <f t="shared" si="5"/>
+        <v>3</v>
       </c>
       <c r="F10">
-        <f t="shared" si="5"/>
-        <v>-1.6460046172142029E-3</v>
+        <f t="shared" si="6"/>
+        <v>-3.7718331721281473E-6</v>
       </c>
       <c r="G10">
-        <f t="shared" si="6"/>
-        <v>1.953125E-3</v>
+        <f t="shared" si="7"/>
+        <v>3.3840951133567998E-6</v>
       </c>
       <c r="H10">
         <v>0.01</v>
       </c>
       <c r="I10">
-        <f t="shared" si="7"/>
-        <v>0.681640625</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+        <f t="shared" si="8"/>
+        <v>0.3221842155843514</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
-        <f t="shared" ref="A11:A17" si="8">IF(D10*F10&lt;0,A10,C10)</f>
-        <v>0.681640625</v>
+        <f t="shared" si="1"/>
+        <v>0.3221842155843514</v>
       </c>
       <c r="B11">
-        <f t="shared" ref="B11:B17" si="9">IF(D10*F10&lt;0,C10,B10)</f>
-        <v>0.68359375</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="C11">
-        <f t="shared" ref="C11:C17" si="10">(A11+B11)/2</f>
-        <v>0.6826171875</v>
+        <f t="shared" si="3"/>
+        <v>0.32218506778596673</v>
       </c>
       <c r="D11">
-        <f t="shared" ref="D11:D17" si="11">(A11^3 )+A11 -1</f>
-        <v>-1.6460046172142029E-3</v>
+        <f t="shared" si="4"/>
+        <v>-3.7718331721281473E-6</v>
       </c>
       <c r="E11">
-        <f t="shared" ref="E11:E17" si="12">(B11^3)+B11-1</f>
-        <v>3.0373930931091309E-3</v>
+        <f t="shared" si="5"/>
+        <v>3</v>
       </c>
       <c r="F11">
-        <f t="shared" ref="F11:F17" si="13">(C11^3)+C11 -1</f>
-        <v>6.9374125450849533E-4</v>
+        <f t="shared" si="6"/>
+        <v>-9.4984521825658419E-7</v>
       </c>
       <c r="G11">
-        <f t="shared" ref="G11:G17" si="14">ABS(C10-C11)</f>
-        <v>9.765625E-4</v>
+        <f t="shared" si="7"/>
+        <v>8.5220161533117178E-7</v>
       </c>
       <c r="H11">
         <v>0.01</v>
       </c>
       <c r="I11">
-        <f t="shared" si="7"/>
-        <v>0.6826171875</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+        <f t="shared" si="8"/>
+        <v>0.32218506778596673</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
-        <f t="shared" si="8"/>
-        <v>0.681640625</v>
+        <f t="shared" si="1"/>
+        <v>0.32218506778596673</v>
       </c>
       <c r="B12">
-        <f t="shared" si="9"/>
-        <v>0.6826171875</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="C12">
-        <f t="shared" si="10"/>
-        <v>0.68212890625</v>
+        <f t="shared" si="3"/>
+        <v>0.3221852823923228</v>
       </c>
       <c r="D12">
-        <f t="shared" si="11"/>
-        <v>-1.6460046172142029E-3</v>
+        <f t="shared" si="4"/>
+        <v>-9.4984521825658419E-7</v>
       </c>
       <c r="E12">
-        <f t="shared" si="12"/>
-        <v>6.9374125450849533E-4</v>
+        <f t="shared" si="5"/>
+        <v>3</v>
       </c>
       <c r="F12">
-        <f t="shared" si="13"/>
-        <v>-4.7661957796663046E-4</v>
+        <f t="shared" si="6"/>
+        <v>-2.3919561442653503E-7</v>
       </c>
       <c r="G12">
-        <f t="shared" si="14"/>
-        <v>4.8828125E-4</v>
+        <f t="shared" si="7"/>
+        <v>2.1460635607484235E-7</v>
       </c>
       <c r="H12">
         <v>0.01</v>
       </c>
       <c r="I12">
-        <f t="shared" si="7"/>
-        <v>0.68212890625</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+        <f t="shared" si="8"/>
+        <v>0.3221852823923228</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
-        <f t="shared" si="8"/>
-        <v>0.68212890625</v>
+        <f t="shared" si="1"/>
+        <v>0.3221852823923228</v>
       </c>
       <c r="B13">
-        <f t="shared" si="9"/>
-        <v>0.6826171875</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="C13">
-        <f t="shared" si="10"/>
-        <v>0.682373046875</v>
+        <f t="shared" si="3"/>
+        <v>0.32218533643575442</v>
       </c>
       <c r="D13">
-        <f t="shared" si="11"/>
-        <v>-4.7661957796663046E-4</v>
+        <f t="shared" si="4"/>
+        <v>-2.3919561442653503E-7</v>
       </c>
       <c r="E13">
-        <f t="shared" si="12"/>
-        <v>6.9374125450849533E-4</v>
+        <f t="shared" si="5"/>
+        <v>3</v>
       </c>
       <c r="F13">
-        <f t="shared" si="13"/>
-        <v>1.0843882046174258E-4</v>
+        <f t="shared" si="6"/>
+        <v>-6.023564802504211E-8</v>
       </c>
       <c r="G13">
-        <f t="shared" si="14"/>
-        <v>2.44140625E-4</v>
+        <f t="shared" si="7"/>
+        <v>5.4043431618744364E-8</v>
       </c>
       <c r="H13">
         <v>0.01</v>
       </c>
       <c r="I13">
-        <f t="shared" si="7"/>
-        <v>0.682373046875</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+        <f t="shared" si="8"/>
+        <v>0.32218533643575442</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
-        <f t="shared" si="8"/>
-        <v>0.68212890625</v>
+        <f t="shared" si="1"/>
+        <v>0.32218533643575442</v>
       </c>
       <c r="B14">
-        <f t="shared" si="9"/>
-        <v>0.682373046875</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="C14">
-        <f t="shared" si="10"/>
-        <v>0.6822509765625</v>
+        <f t="shared" si="3"/>
+        <v>0.32218535004528931</v>
       </c>
       <c r="D14">
-        <f t="shared" si="11"/>
-        <v>-4.7661957796663046E-4</v>
+        <f t="shared" si="4"/>
+        <v>-6.023564802504211E-8</v>
       </c>
       <c r="E14">
-        <f t="shared" si="12"/>
-        <v>1.0843882046174258E-4</v>
+        <f t="shared" si="5"/>
+        <v>3</v>
       </c>
       <c r="F14">
-        <f t="shared" si="13"/>
-        <v>-1.8412087774777319E-4</v>
+        <f t="shared" si="6"/>
+        <v>-1.5168895584061204E-8</v>
       </c>
       <c r="G14">
-        <f t="shared" si="14"/>
-        <v>1.220703125E-4</v>
+        <f t="shared" si="7"/>
+        <v>1.3609534887937258E-8</v>
       </c>
       <c r="H14">
         <v>0.01</v>
       </c>
       <c r="I14">
-        <f t="shared" si="7"/>
-        <v>0.6822509765625</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+        <f t="shared" si="8"/>
+        <v>0.32218535004528931</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
-        <f t="shared" si="8"/>
-        <v>0.6822509765625</v>
+        <f t="shared" si="1"/>
+        <v>0.32218535004528931</v>
       </c>
       <c r="B15">
-        <f t="shared" si="9"/>
-        <v>0.682373046875</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="C15">
-        <f t="shared" si="10"/>
-        <v>0.68231201171875</v>
+        <f t="shared" si="3"/>
+        <v>0.32218535347252253</v>
       </c>
       <c r="D15">
-        <f t="shared" si="11"/>
-        <v>-1.8412087774777319E-4</v>
+        <f t="shared" si="4"/>
+        <v>-1.5168895584061204E-8</v>
       </c>
       <c r="E15">
-        <f t="shared" si="12"/>
-        <v>1.0843882046174258E-4</v>
+        <f t="shared" si="5"/>
+        <v>3</v>
       </c>
       <c r="F15">
-        <f t="shared" si="13"/>
-        <v>-3.7848654073968646E-5</v>
+        <f t="shared" si="6"/>
+        <v>-3.8199204910327467E-9</v>
       </c>
       <c r="G15">
-        <f t="shared" si="14"/>
-        <v>6.103515625E-5</v>
+        <f t="shared" si="7"/>
+        <v>3.427233219444048E-9</v>
       </c>
       <c r="H15">
         <v>0.01</v>
       </c>
       <c r="I15">
-        <f t="shared" si="7"/>
-        <v>0.68231201171875</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+        <f t="shared" si="8"/>
+        <v>0.32218535347252253</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
-        <f t="shared" si="8"/>
-        <v>0.68231201171875</v>
+        <f t="shared" si="1"/>
+        <v>0.32218535347252253</v>
       </c>
       <c r="B16">
-        <f t="shared" si="9"/>
-        <v>0.682373046875</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="C16">
-        <f t="shared" si="10"/>
-        <v>0.682342529296875</v>
+        <f t="shared" si="3"/>
+        <v>0.32218535433558854</v>
       </c>
       <c r="D16">
-        <f t="shared" si="11"/>
-        <v>-3.7848654073968646E-5</v>
+        <f t="shared" si="4"/>
+        <v>-3.8199204910327467E-9</v>
       </c>
       <c r="E16">
-        <f t="shared" si="12"/>
-        <v>1.0843882046174258E-4</v>
+        <f t="shared" si="5"/>
+        <v>3</v>
       </c>
       <c r="F16">
-        <f t="shared" si="13"/>
-        <v>3.5293176750883504E-5</v>
+        <f t="shared" si="6"/>
+        <v>-9.6195496013251613E-10</v>
       </c>
       <c r="G16">
-        <f t="shared" si="14"/>
-        <v>3.0517578125E-5</v>
+        <f t="shared" si="7"/>
+        <v>8.6306600755037266E-10</v>
       </c>
       <c r="H16">
         <v>0.01</v>
       </c>
       <c r="I16">
-        <f t="shared" si="7"/>
-        <v>0.682342529296875</v>
+        <f t="shared" si="8"/>
+        <v>0.32218535433558854</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
-        <f t="shared" si="8"/>
-        <v>0.68231201171875</v>
+        <f t="shared" si="1"/>
+        <v>0.32218535433558854</v>
       </c>
       <c r="B17">
-        <f t="shared" si="9"/>
-        <v>0.682342529296875</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="C17">
-        <f t="shared" si="10"/>
-        <v>0.6823272705078125</v>
+        <f t="shared" si="3"/>
+        <v>0.3221853545529309</v>
       </c>
       <c r="D17">
-        <f t="shared" si="11"/>
-        <v>-3.7848654073968646E-5</v>
+        <f t="shared" si="4"/>
+        <v>-9.6195496013251613E-10</v>
       </c>
       <c r="E17">
-        <f t="shared" si="12"/>
-        <v>3.5293176750883504E-5</v>
+        <f t="shared" si="5"/>
+        <v>3</v>
       </c>
       <c r="F17">
-        <f t="shared" si="13"/>
-        <v>-1.278215261635296E-6</v>
+        <f t="shared" si="6"/>
+        <v>-2.4224522388038849E-10</v>
       </c>
       <c r="G17">
-        <f t="shared" si="14"/>
-        <v>1.52587890625E-5</v>
+        <f t="shared" si="7"/>
+        <v>2.1734236632653392E-10</v>
       </c>
       <c r="H17">
         <v>0.01</v>
       </c>
       <c r="I17">
-        <f t="shared" si="7"/>
-        <v>0.6823272705078125</v>
+        <f t="shared" si="8"/>
+        <v>0.3221853545529309</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <f t="shared" si="1"/>
+        <v>0.3221853545529309</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="3"/>
+        <v>0.32218535460766334</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="4"/>
+        <v>-2.4224522388038849E-10</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="6"/>
+        <v>-6.1003646578683401E-11</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="7"/>
+        <v>5.4732440801785742E-11</v>
+      </c>
+      <c r="H18">
+        <v>0.01</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="8"/>
+        <v>0.32218535460766334</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <f t="shared" si="1"/>
+        <v>0.32218535460766334</v>
+      </c>
+      <c r="B19">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="3"/>
+        <v>0.32218535462144637</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="4"/>
+        <v>-6.1003646578683401E-11</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="6"/>
+        <v>-1.5362378036343216E-11</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="7"/>
+        <v>1.37830302726627E-11</v>
+      </c>
+      <c r="H19">
+        <v>0.01</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="8"/>
+        <v>0.32218535462144637</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <f t="shared" si="1"/>
+        <v>0.32218535462144637</v>
+      </c>
+      <c r="B20">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="3"/>
+        <v>0.32218535462491732</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="4"/>
+        <v>-1.5362378036343216E-11</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="6"/>
+        <v>-3.8686831516088205E-12</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="7"/>
+        <v>3.4709457530368582E-12</v>
+      </c>
+      <c r="H20">
+        <v>0.01</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="8"/>
+        <v>0.32218535462491732</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <f t="shared" si="1"/>
+        <v>0.32218535462491732</v>
+      </c>
+      <c r="B21">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="3"/>
+        <v>0.32218535462579134</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="4"/>
+        <v>-3.8686831516088205E-12</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="6"/>
+        <v>-9.7433172641103738E-13</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="7"/>
+        <v>8.7402307613615449E-13</v>
+      </c>
+      <c r="H21">
+        <v>0.01</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="8"/>
+        <v>0.32218535462579134</v>
       </c>
     </row>
   </sheetData>
@@ -1083,7 +2468,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFF8D236-D571-40AC-9BC0-67D35102D9C7}">
   <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1527,297 +2912,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{854C4007-B242-4866-BDB4-E9D073D572EC}">
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <f>A2-D2*(B2-A2)/(E2-D2)</f>
-        <v>0.5</v>
-      </c>
-      <c r="D2">
-        <f>(A2^3 )+A2 -1</f>
-        <v>-1</v>
-      </c>
-      <c r="E2">
-        <f>(B2^3)+B2-1</f>
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <f>(C2^3)+C2 -1</f>
-        <v>-0.375</v>
-      </c>
-      <c r="H2">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <f>IF(D2*F2&lt;0,A2,C2)</f>
-        <v>0.5</v>
-      </c>
-      <c r="B3">
-        <f>IF(D2*F2&lt;0,C2,B2)</f>
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <f>A3-D3*(B3-A3)/(E3-D3)</f>
-        <v>0.63636363636363635</v>
-      </c>
-      <c r="D3">
-        <f>(A3^3 )+A3 -1</f>
-        <v>-0.375</v>
-      </c>
-      <c r="E3">
-        <f>(B3^3)+B3-1</f>
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <f>(C3^3)+C3 -1</f>
-        <v>-0.10593538692712245</v>
-      </c>
-      <c r="G3">
-        <f>ABS(C2-C3)</f>
-        <v>0.13636363636363635</v>
-      </c>
-      <c r="H3">
-        <v>0.01</v>
-      </c>
-      <c r="I3" t="str">
-        <f>IF(G3&lt;H3, C3, "Не ответ")</f>
-        <v>Не ответ</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <f t="shared" ref="A4:A8" si="0">IF(D3*F3&lt;0,A3,C3)</f>
-        <v>0.63636363636363635</v>
-      </c>
-      <c r="B4">
-        <f t="shared" ref="B4:B8" si="1">IF(D3*F3&lt;0,C3,B3)</f>
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <f t="shared" ref="C4:C8" si="2">A4-D4*(B4-A4)/(E4-D4)</f>
-        <v>0.67119565217391308</v>
-      </c>
-      <c r="D4">
-        <f t="shared" ref="D4:D8" si="3">(A4^3 )+A4 -1</f>
-        <v>-0.10593538692712245</v>
-      </c>
-      <c r="E4">
-        <f t="shared" ref="E4:E8" si="4">(B4^3)+B4-1</f>
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <f t="shared" ref="F4:F8" si="5">(C4^3)+C4 -1</f>
-        <v>-2.6428287870109646E-2</v>
-      </c>
-      <c r="G4">
-        <f t="shared" ref="G4:G8" si="6">ABS(C3-C4)</f>
-        <v>3.4832015810276729E-2</v>
-      </c>
-      <c r="H4">
-        <v>1.01</v>
-      </c>
-      <c r="I4">
-        <f t="shared" ref="I4:I8" si="7">IF(G4&lt;H4, C4, "Не ответ")</f>
-        <v>0.67119565217391308</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <f t="shared" si="0"/>
-        <v>0.67119565217391308</v>
-      </c>
-      <c r="B5">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <f t="shared" si="2"/>
-        <v>0.67966164639872462</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="3"/>
-        <v>-2.6428287870109646E-2</v>
-      </c>
-      <c r="E5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <f t="shared" si="5"/>
-        <v>-6.3754842100549602E-3</v>
-      </c>
-      <c r="G5">
-        <f t="shared" si="6"/>
-        <v>8.465994224811535E-3</v>
-      </c>
-      <c r="H5">
-        <v>2.0099999999999998</v>
-      </c>
-      <c r="I5">
-        <f t="shared" si="7"/>
-        <v>0.67966164639872462</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <f t="shared" si="0"/>
-        <v>0.67966164639872462</v>
-      </c>
-      <c r="B6">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <f t="shared" si="2"/>
-        <v>0.68169102027289352</v>
-      </c>
-      <c r="D6">
-        <f t="shared" si="3"/>
-        <v>-6.3754842100549602E-3</v>
-      </c>
-      <c r="E6">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <f t="shared" si="5"/>
-        <v>-1.5253580878831219E-3</v>
-      </c>
-      <c r="G6">
-        <f t="shared" si="6"/>
-        <v>2.0293738741689049E-3</v>
-      </c>
-      <c r="H6">
-        <v>3.01</v>
-      </c>
-      <c r="I6">
-        <f t="shared" si="7"/>
-        <v>0.68169102027289352</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <f t="shared" si="0"/>
-        <v>0.68169102027289352</v>
-      </c>
-      <c r="B7">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <f t="shared" si="2"/>
-        <v>0.68217581596253996</v>
-      </c>
-      <c r="D7">
-        <f t="shared" si="3"/>
-        <v>-1.5253580878831219E-3</v>
-      </c>
-      <c r="E7">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <f t="shared" si="5"/>
-        <v>-3.6422411632108798E-4</v>
-      </c>
-      <c r="G7">
-        <f t="shared" si="6"/>
-        <v>4.8479568964643338E-4</v>
-      </c>
-      <c r="H7">
-        <v>4.01</v>
-      </c>
-      <c r="I7">
-        <f t="shared" si="7"/>
-        <v>0.68217581596253996</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <f t="shared" si="0"/>
-        <v>0.68217581596253996</v>
-      </c>
-      <c r="B8">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <f t="shared" si="2"/>
-        <v>0.68229153304816326</v>
-      </c>
-      <c r="D8">
-        <f t="shared" si="3"/>
-        <v>-3.6422411632108798E-4</v>
-      </c>
-      <c r="E8">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <f t="shared" si="5"/>
-        <v>-8.6927981931106402E-5</v>
-      </c>
-      <c r="G8">
-        <f t="shared" si="6"/>
-        <v>1.1571708562330141E-4</v>
-      </c>
-      <c r="H8">
-        <v>5.01</v>
-      </c>
-      <c r="I8">
-        <f t="shared" si="7"/>
-        <v>0.68229153304816326</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56602285-2A94-4A94-BBD5-6F90D6E3E1AB}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1839,14 +2936,18 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="B2">
-        <f>A2^3 + A2-1</f>
-        <v>1</v>
+        <f>A2^3+3*A2-1</f>
+        <v>0.625</v>
+      </c>
+      <c r="C2">
+        <f>ABS(B2)/D2</f>
+        <v>0.10416666666666667</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E2">
         <v>0.01</v>
@@ -1858,18 +2959,18 @@
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>A2-B2/D2</f>
-        <v>0.75</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="B3">
-        <f>A3^3 + A3-1</f>
-        <v>0.171875</v>
+        <f>A3^3+3*A3-1</f>
+        <v>0.24952076099537046</v>
       </c>
       <c r="C3">
-        <f>ABS(A2-A3)</f>
-        <v>0.25</v>
+        <f>ABS(B3)/D3</f>
+        <v>4.1586793499228412E-2</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E3">
         <v>0.01</v>
@@ -1881,122 +2982,266 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
-        <f t="shared" ref="A4:A8" si="0">A3-B3/D3</f>
-        <v>0.70703125</v>
+        <f t="shared" ref="A4:A14" si="0">A3-B3/D3</f>
+        <v>0.35424653983410492</v>
       </c>
       <c r="B4">
-        <f t="shared" ref="B4:B8" si="1">A4^3 + A4-1</f>
-        <v>6.047135591506958E-2</v>
+        <f t="shared" ref="B4:B14" si="1">A4^3+3*A4-1</f>
+        <v>0.10719423422521901</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:C8" si="2">ABS(A3-A4)</f>
-        <v>4.296875E-2</v>
+        <f t="shared" ref="C4:C14" si="2">ABS(B4)/D4</f>
+        <v>1.7865705704203167E-2</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>0.01</v>
       </c>
       <c r="F4" t="str">
-        <f t="shared" ref="F4:F8" si="3">IF(C4&lt;E4, A4, "Не ответ")</f>
+        <f t="shared" ref="F4:F14" si="3">IF(C4&lt;E4, A4, "Не ответ")</f>
         <v>Не ответ</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <f t="shared" si="0"/>
-        <v>0.6919134110212326</v>
+        <v>0.33638083412990177</v>
       </c>
       <c r="B5">
         <f t="shared" si="1"/>
-        <v>2.3162921551521887E-2</v>
+        <v>4.7204688589639332E-2</v>
       </c>
       <c r="C5">
         <f t="shared" si="2"/>
-        <v>1.5117838978767395E-2</v>
+        <v>7.867448098273222E-3</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <v>0.01</v>
       </c>
-      <c r="F5" t="str">
-        <f t="shared" si="3"/>
-        <v>Не ответ</v>
+      <c r="F5" s="1">
+        <f t="shared" si="3"/>
+        <v>0.33638083412990177</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" si="0"/>
-        <v>0.68612268063335213</v>
+        <v>0.32851338603162855</v>
       </c>
       <c r="B6">
         <f t="shared" si="1"/>
-        <v>9.1247666552043416E-3</v>
+        <v>2.0993665946850593E-2</v>
       </c>
       <c r="C6">
         <f t="shared" si="2"/>
-        <v>5.7907303878804717E-3</v>
+        <v>3.4989443244750986E-3</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>0.01</v>
       </c>
-      <c r="F6" s="1">
-        <f t="shared" si="3"/>
-        <v>0.68612268063335213</v>
+      <c r="F6">
+        <f t="shared" si="3"/>
+        <v>0.32851338603162855</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="0"/>
-        <v>0.68384148896955099</v>
+        <v>0.32501444170715343</v>
       </c>
       <c r="B7">
         <f t="shared" si="1"/>
-        <v>3.6325635136154055E-3</v>
+        <v>9.3760265407663024E-3</v>
       </c>
       <c r="C7">
         <f t="shared" si="2"/>
-        <v>2.2811916638011409E-3</v>
+        <v>1.562671090127717E-3</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E7">
         <v>0.01</v>
       </c>
       <c r="F7">
         <f t="shared" si="3"/>
-        <v>0.68384148896955099</v>
+        <v>0.32501444170715343</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="0"/>
-        <v>0.68293334809114714</v>
+        <v>0.32345177061702574</v>
       </c>
       <c r="B8">
         <f t="shared" si="1"/>
-        <v>1.4520670465598684E-3</v>
+        <v>4.1951750430861967E-3</v>
       </c>
       <c r="C8">
         <f t="shared" si="2"/>
-        <v>9.0814087840385138E-4</v>
+        <v>6.9919584051436612E-4</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E8">
         <v>0.01</v>
       </c>
       <c r="F8">
         <f t="shared" si="3"/>
-        <v>0.68293334809114714</v>
+        <v>0.32345177061702574</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <f t="shared" si="0"/>
+        <v>0.32275257477651137</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="1"/>
+        <v>1.8786097574075011E-3</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="2"/>
+        <v>3.1310162623458354E-4</v>
+      </c>
+      <c r="D9">
+        <v>6</v>
+      </c>
+      <c r="E9">
+        <v>0.01</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="3"/>
+        <v>0.32275257477651137</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <f t="shared" si="0"/>
+        <v>0.32243947315027677</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="1"/>
+        <v>8.4155310805233974E-4</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="2"/>
+        <v>1.4025885134205662E-4</v>
+      </c>
+      <c r="D10">
+        <v>6</v>
+      </c>
+      <c r="E10">
+        <v>0.01</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="3"/>
+        <v>0.32243947315027677</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <f t="shared" si="0"/>
+        <v>0.32229921429893471</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="1"/>
+        <v>3.7704861490883701E-4</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="2"/>
+        <v>6.2841435818139502E-5</v>
+      </c>
+      <c r="D11">
+        <v>6</v>
+      </c>
+      <c r="E11">
+        <v>0.01</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="3"/>
+        <v>0.32229921429893471</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>0.32223637286311657</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="1"/>
+        <v>1.6894482685247958E-4</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="2"/>
+        <v>2.8157471142079931E-5</v>
+      </c>
+      <c r="D12">
+        <v>6</v>
+      </c>
+      <c r="E12">
+        <v>0.01</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="3"/>
+        <v>0.32223637286311657</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <f t="shared" si="0"/>
+        <v>0.32220821539197447</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="1"/>
+        <v>7.5701878680112245E-5</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="2"/>
+        <v>1.2616979780018708E-5</v>
+      </c>
+      <c r="D13">
+        <v>6</v>
+      </c>
+      <c r="E13">
+        <v>0.01</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="3"/>
+        <v>0.32220821539197447</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <f t="shared" si="0"/>
+        <v>0.32219559841219447</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="1"/>
+        <v>3.3921479318355097E-5</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="2"/>
+        <v>5.6535798863925164E-6</v>
+      </c>
+      <c r="D14">
+        <v>6</v>
+      </c>
+      <c r="E14">
+        <v>0.01</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="3"/>
+        <v>0.32219559841219447</v>
       </c>
     </row>
   </sheetData>
@@ -2007,7 +3252,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E20FAE7A-A746-4C8B-8E4C-9FB90CC4728C}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.140625" style="4" bestFit="1" customWidth="1"/>
@@ -2032,36 +3277,44 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="B2" s="4">
-        <f>A2^3 + A2-1</f>
-        <v>1</v>
+        <f>A2^3+3*A2-1</f>
+        <v>0.625</v>
       </c>
       <c r="C2">
-        <f>3*A2^2+1</f>
-        <v>4</v>
+        <f>3*A2^2+3</f>
+        <v>3.75</v>
+      </c>
+      <c r="D2">
+        <f>ABS(B2/C2)</f>
+        <v>0.16666666666666666</v>
       </c>
       <c r="E2">
         <v>0.01</v>
+      </c>
+      <c r="F2">
+        <f ca="1">IF(E2&lt;F2,D2,"Не ответ")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>A2-B2/C2</f>
-        <v>0.75</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="B3" s="4">
-        <f>A3^3 + A3-1</f>
-        <v>0.171875</v>
+        <f>A3^3+3*A3-1</f>
+        <v>3.7037037037036979E-2</v>
       </c>
       <c r="C3">
-        <f>3*A3^2+1</f>
-        <v>2.6875</v>
+        <f>3*A3^2+3</f>
+        <v>3.3333333333333335</v>
       </c>
       <c r="D3">
-        <f>ABS(A2-A3)</f>
-        <v>0.25</v>
+        <f>ABS(B3/C3)</f>
+        <v>1.1111111111111094E-2</v>
       </c>
       <c r="E3">
         <v>0.01</v>
@@ -2073,83 +3326,83 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
-        <f t="shared" ref="A4:A8" si="0">A3-B3/C3</f>
-        <v>0.68604651162790697</v>
+        <f t="shared" ref="A4:A15" si="0">A3-B3/C3</f>
+        <v>0.3222222222222223</v>
       </c>
       <c r="B4" s="4">
-        <f t="shared" ref="B4:B8" si="1">A4^3 + A4-1</f>
-        <v>8.9410366382833839E-3</v>
+        <f t="shared" ref="B4:B15" si="1">A4^3+3*A4-1</f>
+        <v>1.2208504801125564E-4</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:C8" si="2">3*A4^2+1</f>
-        <v>2.4119794483504595</v>
+        <f t="shared" ref="C4:C15" si="2">3*A4^2+3</f>
+        <v>3.3114814814814815</v>
       </c>
       <c r="D4">
-        <f t="shared" ref="D4:D8" si="3">ABS(A3-A4)</f>
-        <v>6.3953488372093026E-2</v>
+        <f t="shared" ref="D4:D15" si="3">ABS(B4/C4)</f>
+        <v>3.686719937707082E-5</v>
       </c>
       <c r="E4">
         <v>0.01</v>
       </c>
-      <c r="F4" t="str">
-        <f t="shared" ref="F4:F8" si="4">IF(D4&lt;E4, A4, "Не ответ")</f>
-        <v>Не ответ</v>
+      <c r="F4">
+        <f t="shared" ref="F4:F15" si="4">IF(D4&lt;E4, A4, "Не ответ")</f>
+        <v>0.3222222222222223</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <f t="shared" si="0"/>
-        <v>0.6823395825973142</v>
+        <v>0.32218535502284523</v>
       </c>
       <c r="B5" s="4">
         <f t="shared" si="1"/>
-        <v>2.8230621685665369E-5</v>
+        <v>1.3138339305385216E-9</v>
       </c>
       <c r="C5">
         <f t="shared" si="2"/>
-        <v>2.3967619179372308</v>
+        <v>3.3114102089735904</v>
       </c>
       <c r="D5">
         <f t="shared" si="3"/>
-        <v>3.706929030592776E-3</v>
+        <v>3.9675964245630552E-10</v>
       </c>
       <c r="E5">
         <v>0.01</v>
       </c>
       <c r="F5">
         <f t="shared" si="4"/>
-        <v>0.6823395825973142</v>
+        <v>0.32218535502284523</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" si="0"/>
-        <v>0.68232780394651271</v>
+        <v>0.32218535462608561</v>
       </c>
       <c r="B6" s="4">
         <f t="shared" si="1"/>
-        <v>2.8399460560990519E-10</v>
+        <v>0</v>
       </c>
       <c r="C6">
         <f t="shared" si="2"/>
-        <v>2.3967136961154121</v>
+        <v>3.3114102082066097</v>
       </c>
       <c r="D6">
         <f t="shared" si="3"/>
-        <v>1.1778650801486101E-5</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0.01</v>
       </c>
       <c r="F6">
         <f t="shared" si="4"/>
-        <v>0.68232780394651271</v>
+        <v>0.32218535462608561</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="0"/>
-        <v>0.68232780382801939</v>
+        <v>0.32218535462608561</v>
       </c>
       <c r="B7" s="4">
         <f t="shared" si="1"/>
@@ -2157,24 +3410,24 @@
       </c>
       <c r="C7">
         <f t="shared" si="2"/>
-        <v>2.3967136956303046</v>
+        <v>3.3114102082066097</v>
       </c>
       <c r="D7">
         <f t="shared" si="3"/>
-        <v>1.1849332626212572E-10</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0.01</v>
       </c>
       <c r="F7">
         <f t="shared" si="4"/>
-        <v>0.68232780382801939</v>
+        <v>0.32218535462608561</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="0"/>
-        <v>0.68232780382801939</v>
+        <v>0.32218535462608561</v>
       </c>
       <c r="B8" s="4">
         <f t="shared" si="1"/>
@@ -2182,7 +3435,7 @@
       </c>
       <c r="C8">
         <f t="shared" si="2"/>
-        <v>2.3967136956303046</v>
+        <v>3.3114102082066097</v>
       </c>
       <c r="D8">
         <f t="shared" si="3"/>
@@ -2193,7 +3446,182 @@
       </c>
       <c r="F8">
         <f t="shared" si="4"/>
-        <v>0.68232780382801939</v>
+        <v>0.32218535462608561</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <f t="shared" si="0"/>
+        <v>0.32218535462608561</v>
+      </c>
+      <c r="B9" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="2"/>
+        <v>3.3114102082066097</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0.01</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="4"/>
+        <v>0.32218535462608561</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <f t="shared" si="0"/>
+        <v>0.32218535462608561</v>
+      </c>
+      <c r="B10" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="2"/>
+        <v>3.3114102082066097</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0.01</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="4"/>
+        <v>0.32218535462608561</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <f t="shared" si="0"/>
+        <v>0.32218535462608561</v>
+      </c>
+      <c r="B11" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="2"/>
+        <v>3.3114102082066097</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0.01</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="4"/>
+        <v>0.32218535462608561</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>0.32218535462608561</v>
+      </c>
+      <c r="B12" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="2"/>
+        <v>3.3114102082066097</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0.01</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="4"/>
+        <v>0.32218535462608561</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <f t="shared" si="0"/>
+        <v>0.32218535462608561</v>
+      </c>
+      <c r="B13" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="2"/>
+        <v>3.3114102082066097</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0.01</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="4"/>
+        <v>0.32218535462608561</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <f t="shared" si="0"/>
+        <v>0.32218535462608561</v>
+      </c>
+      <c r="B14" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="2"/>
+        <v>3.3114102082066097</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0.01</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="4"/>
+        <v>0.32218535462608561</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <f t="shared" si="0"/>
+        <v>0.32218535462608561</v>
+      </c>
+      <c r="B15" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="2"/>
+        <v>3.3114102082066097</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0.01</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="4"/>
+        <v>0.32218535462608561</v>
       </c>
     </row>
   </sheetData>
